--- a/outputs/10747.xlsx
+++ b/outputs/10747.xlsx
@@ -133,16 +133,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -338,217 +342,217 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>101010</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>-5300</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>12000</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F3" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="J3" s="0" t="n">
+      <c r="J3" s="1" t="n">
         <v>101010</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <f aca="false">+C4</f>
         <v>-10600</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <f aca="false">+E4</f>
         <v>4000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>101010</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <f aca="false">+C3*2</f>
         <v>-10600</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <f aca="false">+D3*2</f>
         <v>24000</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <f aca="false">+E3*2</f>
         <v>4000</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <f aca="false">+F3*2</f>
         <v>400</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="J4" s="0" t="n">
+      <c r="J4" s="1" t="n">
         <v>202020</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <f aca="false">+C6</f>
         <v>-4240</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <f aca="false">+E6</f>
         <v>1600</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>2011</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>101010</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <f aca="false">+C4*1.1</f>
         <v>-11660</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <f aca="false">+D4*1.1</f>
         <v>26400</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <f aca="false">+E4*1.1</f>
         <v>4400</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <f aca="false">+F4*1.1</f>
         <v>440</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>2013</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>202020</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <f aca="false">+C3*0.8</f>
         <v>-4240</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <f aca="false">+D3*0.8</f>
         <v>9600</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <f aca="false">+E3*0.8</f>
         <v>1600</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <f aca="false">+F3*0.8</f>
         <v>160</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <f aca="false">SUMIFS(C3:C8,A3:A8,I3,B3:B8,J3)</f>
         <v>-10600</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>2012</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>202020</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <f aca="false">+C6*2</f>
         <v>-8480</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <f aca="false">+D6*2</f>
         <v>19200</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <f aca="false">+E6*2</f>
         <v>3200</v>
       </c>
-      <c r="F7" s="0" t="n">
+      <c r="F7" s="1" t="n">
         <f aca="false">+F6*2</f>
         <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>2011</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>202020</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <f aca="false">+C7*1.1</f>
         <v>-9328</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <f aca="false">+D7*1.1</f>
         <v>21120</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <f aca="false">+E7*1.1</f>
         <v>3520</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <f aca="false">+F7*1.1</f>
         <v>352</v>
       </c>

--- a/outputs/10747.xlsx
+++ b/outputs/10747.xlsx
@@ -505,7 +505,7 @@
         <v>7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <f aca="false">SUMIFS(C3:C8,A3:A8,I3,B3:B8,J3)</f>
+        <f aca="false">SUMIFS($C$3:$C$8,$A$3:$A$8,$I3,$B$3:$B$8,$J3)</f>
         <v>-10600</v>
       </c>
     </row>
